--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260918.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260918.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.03%</t>
+          <t>26.72%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.18%</t>
+          <t>8.00%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.87%</t>
+          <t>7.97%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.65%</t>
+          <t>6.72%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.28%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>4.39%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1078,117 +1078,117 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>62,777,359</t>
+          <t>18,455</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>18,455</t>
+          <t>57,898,546</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>126,205</t>
+          <t>9,536</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>15,871</t>
+          <t>126,205</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>9,536</t>
+          <t>15,871</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
